--- a/data/trans_orig/P2C_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79576</t>
+          <t>80441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110679</t>
+          <t>111242</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95961</t>
+          <t>95149</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129899</t>
+          <t>129181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>182557</t>
+          <t>183856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230082</t>
+          <t>229810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162331</t>
+          <t>161768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>193434</t>
+          <t>192569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130939</t>
+          <t>131657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164877</t>
+          <t>165689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>303766</t>
+          <t>304038</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>351291</t>
+          <t>349992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95679</t>
+          <t>95210</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133645</t>
+          <t>136187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135393</t>
+          <t>135248</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176968</t>
+          <t>176604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241548</t>
+          <t>241004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>298462</t>
+          <t>299249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359430</t>
+          <t>356888</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397396</t>
+          <t>397865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326981</t>
+          <t>327345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368556</t>
+          <t>368701</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>698562</t>
+          <t>697775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755476</t>
+          <t>756020</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91737</t>
+          <t>91497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124870</t>
+          <t>126345</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103131</t>
+          <t>103791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139576</t>
+          <t>138099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203789</t>
+          <t>206086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253871</t>
+          <t>253378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>193976</t>
+          <t>192501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227109</t>
+          <t>227349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195836</t>
+          <t>197313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232281</t>
+          <t>231621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>400387</t>
+          <t>400880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>450469</t>
+          <t>448172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87212</t>
+          <t>85976</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121044</t>
+          <t>123287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123975</t>
+          <t>125116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160080</t>
+          <t>158910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>219757</t>
+          <t>221594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270772</t>
+          <t>272407</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237627</t>
+          <t>235384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271459</t>
+          <t>272695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211376</t>
+          <t>212546</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>247481</t>
+          <t>246340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>459355</t>
+          <t>457720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>510370</t>
+          <t>508533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,65%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>35519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60530</t>
+          <t>59363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51106</t>
+          <t>50466</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>77771</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93072</t>
+          <t>92542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127166</t>
+          <t>130327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142778</t>
+          <t>143945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165950</t>
+          <t>167789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130537</t>
+          <t>129897</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156562</t>
+          <t>157202</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283810</t>
+          <t>280649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>317904</t>
+          <t>318434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79992</t>
+          <t>79066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110520</t>
+          <t>110324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67804</t>
+          <t>65532</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98713</t>
+          <t>96483</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>157012</t>
+          <t>154567</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>199143</t>
+          <t>198848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160291</t>
+          <t>160487</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190819</t>
+          <t>191745</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179431</t>
+          <t>181661</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>210340</t>
+          <t>212612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349812</t>
+          <t>350107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>391943</t>
+          <t>394388</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,84%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>154384</t>
+          <t>156569</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200618</t>
+          <t>200626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>225960</t>
+          <t>225839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>276784</t>
+          <t>273610</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>392208</t>
+          <t>394243</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>460837</t>
+          <t>460570</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>414409</t>
+          <t>414401</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>460643</t>
+          <t>458458</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>361435</t>
+          <t>364609</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>412259</t>
+          <t>412380</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>792409</t>
+          <t>792676</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>861038</t>
+          <t>859003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>190586</t>
+          <t>190068</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>240721</t>
+          <t>240336</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>215546</t>
+          <t>218718</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>266761</t>
+          <t>267843</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>424005</t>
+          <t>419324</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>495495</t>
+          <t>493673</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>503074</t>
+          <t>503459</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>553209</t>
+          <t>553727</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>516750</t>
+          <t>515668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>567965</t>
+          <t>564793</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1031811</t>
+          <t>1033633</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1103301</t>
+          <t>1107982</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,54%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>899229</t>
+          <t>902370</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1010203</t>
+          <t>1007998</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1110807</t>
+          <t>1112673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1218215</t>
+          <t>1224850</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2042280</t>
+          <t>2052399</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2190236</t>
+          <t>2205057</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2266340</t>
+          <t>2268545</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2377314</t>
+          <t>2374173</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2160982</t>
+          <t>2154347</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2268390</t>
+          <t>2266524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4465505</t>
+          <t>4450684</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4613461</t>
+          <t>4603342</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115199</t>
+          <t>117639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>152897</t>
+          <t>150863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144025</t>
+          <t>144050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>178097</t>
+          <t>180936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>269959</t>
+          <t>269947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321756</t>
+          <t>317185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141841</t>
+          <t>143875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179539</t>
+          <t>177099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109148</t>
+          <t>106309</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143220</t>
+          <t>143195</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>260227</t>
+          <t>264798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>312024</t>
+          <t>312036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>206692</t>
+          <t>203071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>252418</t>
+          <t>251812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239624</t>
+          <t>239211</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>286962</t>
+          <t>285255</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>460355</t>
+          <t>459885</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>525519</t>
+          <t>526140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>253109</t>
+          <t>253715</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298835</t>
+          <t>302456</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236803</t>
+          <t>238510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>284141</t>
+          <t>284554</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>503773</t>
+          <t>503152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568937</t>
+          <t>569407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126611</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164295</t>
+          <t>163230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155938</t>
+          <t>154641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193429</t>
+          <t>195353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>293162</t>
+          <t>293073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>345911</t>
+          <t>344993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159751</t>
+          <t>160816</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>197435</t>
+          <t>197350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147591</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185082</t>
+          <t>186379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319155</t>
+          <t>320073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371904</t>
+          <t>371993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164778</t>
+          <t>164909</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207626</t>
+          <t>206403</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>197348</t>
+          <t>196713</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236317</t>
+          <t>236852</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>375733</t>
+          <t>374086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>433769</t>
+          <t>435352</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,06%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166356</t>
+          <t>167579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209204</t>
+          <t>209073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152634</t>
+          <t>152099</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191603</t>
+          <t>192238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329164</t>
+          <t>327581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387200</t>
+          <t>388847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86184</t>
+          <t>85582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116506</t>
+          <t>115008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108781</t>
+          <t>108821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139309</t>
+          <t>138665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>204000</t>
+          <t>200353</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245994</t>
+          <t>245585</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96112</t>
+          <t>97610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126434</t>
+          <t>127036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80282</t>
+          <t>80926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110810</t>
+          <t>110770</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186215</t>
+          <t>186624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>228209</t>
+          <t>231856</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107709</t>
+          <t>106240</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140478</t>
+          <t>140177</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>127279</t>
+          <t>127516</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159666</t>
+          <t>160053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>242599</t>
+          <t>243938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>289716</t>
+          <t>290855</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133503</t>
+          <t>133804</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166272</t>
+          <t>167741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>120365</t>
+          <t>119978</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152752</t>
+          <t>152515</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>264296</t>
+          <t>263157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>311413</t>
+          <t>310074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>266196</t>
+          <t>266519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>319709</t>
+          <t>321406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>310965</t>
+          <t>307562</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>364289</t>
+          <t>363395</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>591434</t>
+          <t>595457</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>668134</t>
+          <t>668053</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>343079</t>
+          <t>341382</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>396592</t>
+          <t>396269</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>329564</t>
+          <t>330458</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382888</t>
+          <t>386291</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>688507</t>
+          <t>688588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>765207</t>
+          <t>761184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,11%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>292917</t>
+          <t>294932</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>352488</t>
+          <t>355138</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>385408</t>
+          <t>389886</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>445002</t>
+          <t>444985</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>700446</t>
+          <t>700057</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>780080</t>
+          <t>779444</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>426610</t>
+          <t>423960</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>486181</t>
+          <t>484166</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>378851</t>
+          <t>378868</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>438445</t>
+          <t>433967</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>822871</t>
+          <t>823507</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>902505</t>
+          <t>902894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1478659</t>
+          <t>1475400</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1593946</t>
+          <t>1592229</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1776561</t>
+          <t>1777181</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1901319</t>
+          <t>1901415</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3270192</t>
+          <t>3291292</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3452205</t>
+          <t>3461983</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1832833</t>
+          <t>1834550</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1948120</t>
+          <t>1951379</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1656990</t>
+          <t>1656894</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1781748</t>
+          <t>1781128</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3532883</t>
+          <t>3523105</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3714896</t>
+          <t>3693796</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>94467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131423</t>
+          <t>130460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102506</t>
+          <t>103328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136583</t>
+          <t>138804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206260</t>
+          <t>208111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257009</t>
+          <t>256803</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162338</t>
+          <t>163301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>198188</t>
+          <t>199294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152120</t>
+          <t>149899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186197</t>
+          <t>185375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>325455</t>
+          <t>325661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>376204</t>
+          <t>374353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,27%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115076</t>
+          <t>114031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154562</t>
+          <t>154202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154804</t>
+          <t>158638</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>201226</t>
+          <t>202394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>281967</t>
+          <t>280619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>341918</t>
+          <t>340275</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348013</t>
+          <t>348373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387499</t>
+          <t>388544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321858</t>
+          <t>320690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368280</t>
+          <t>364446</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683741</t>
+          <t>685384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743692</t>
+          <t>745040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70068</t>
+          <t>70218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99427</t>
+          <t>101577</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85535</t>
+          <t>85668</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120673</t>
+          <t>119854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163203</t>
+          <t>163130</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207930</t>
+          <t>207515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>219138</t>
+          <t>216988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>248497</t>
+          <t>248347</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>215636</t>
+          <t>216455</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250774</t>
+          <t>250641</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>446944</t>
+          <t>447359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>491671</t>
+          <t>491744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93436</t>
+          <t>93898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128782</t>
+          <t>130319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134245</t>
+          <t>134841</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172756</t>
+          <t>174004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>237684</t>
+          <t>237340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>290429</t>
+          <t>294161</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241182</t>
+          <t>239645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276528</t>
+          <t>276066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214527</t>
+          <t>213279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>253038</t>
+          <t>252442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>466818</t>
+          <t>463086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519563</t>
+          <t>519907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75426</t>
+          <t>76992</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103934</t>
+          <t>105081</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89122</t>
+          <t>88171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117467</t>
+          <t>116932</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171828</t>
+          <t>172766</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212857</t>
+          <t>213452</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107287</t>
+          <t>106140</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135795</t>
+          <t>134229</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101120</t>
+          <t>101655</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129465</t>
+          <t>130416</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216951</t>
+          <t>216356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257980</t>
+          <t>257042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,8%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63571</t>
+          <t>61764</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91075</t>
+          <t>91484</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75106</t>
+          <t>74569</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106576</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148565</t>
+          <t>146318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189853</t>
+          <t>190570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172048</t>
+          <t>171639</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>199552</t>
+          <t>201359</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>166539</t>
+          <t>166038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>198009</t>
+          <t>198546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>346385</t>
+          <t>345668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>387673</t>
+          <t>389920</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>151841</t>
+          <t>151191</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196755</t>
+          <t>197658</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>225722</t>
+          <t>227142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>276932</t>
+          <t>278123</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>392514</t>
+          <t>390557</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>463370</t>
+          <t>459785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>459803</t>
+          <t>458900</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>504717</t>
+          <t>505367</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>414362</t>
+          <t>413171</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>465572</t>
+          <t>464152</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>884482</t>
+          <t>888067</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>955338</t>
+          <t>957295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>255533</t>
+          <t>251279</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>308968</t>
+          <t>306687</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>344447</t>
+          <t>347754</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>406457</t>
+          <t>404591</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>616687</t>
+          <t>616966</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>696456</t>
+          <t>693369</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>469615</t>
+          <t>471896</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>523050</t>
+          <t>527304</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>419710</t>
+          <t>421576</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>481720</t>
+          <t>478413</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>908294</t>
+          <t>911381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>988063</t>
+          <t>987784</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1007995</t>
+          <t>1008815</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1110714</t>
+          <t>1117687</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1312864</t>
+          <t>1316269</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1434726</t>
+          <t>1436404</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2353086</t>
+          <t>2353450</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2516177</t>
+          <t>2514349</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2283636</t>
+          <t>2276663</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2386355</t>
+          <t>2385535</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2109816</t>
+          <t>2108138</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2231678</t>
+          <t>2228273</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4422715</t>
+          <t>4424543</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4585806</t>
+          <t>4585442</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27009</t>
+          <t>27921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>17739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>32429</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>33345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54319</t>
+          <t>54983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284434</t>
+          <t>283522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300179</t>
+          <t>299820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256583</t>
+          <t>257206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271227</t>
+          <t>271896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>546758</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567708</t>
+          <t>567732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41358</t>
+          <t>41478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73201</t>
+          <t>73724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85227</t>
+          <t>86247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118212</t>
+          <t>116862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>133958</t>
+          <t>135057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>181262</t>
+          <t>179770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>445189</t>
+          <t>444666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>477032</t>
+          <t>476912</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>396757</t>
+          <t>398107</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429742</t>
+          <t>428722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>852097</t>
+          <t>853589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>899401</t>
+          <t>898302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28192</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50852</t>
+          <t>49567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36865</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57545</t>
+          <t>58190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69159</t>
+          <t>71693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101166</t>
+          <t>101943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>265198</t>
+          <t>266483</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287858</t>
+          <t>287377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>291583</t>
+          <t>290938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312263</t>
+          <t>312845</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>564012</t>
+          <t>563235</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>596019</t>
+          <t>593485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65038</t>
+          <t>67761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38242</t>
+          <t>37606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82394</t>
+          <t>83124</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80730</t>
+          <t>78613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138130</t>
+          <t>136445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>247519</t>
+          <t>244796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>277673</t>
+          <t>277621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393324</t>
+          <t>392594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>437476</t>
+          <t>438112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>650144</t>
+          <t>651829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>707544</t>
+          <t>709661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>29430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>34029</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>29802</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54128</t>
+          <t>55320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150660</t>
+          <t>149312</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165076</t>
+          <t>165421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224912</t>
+          <t>224750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>246710</t>
+          <t>245680</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383393</t>
+          <t>382201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407883</t>
+          <t>407719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37496</t>
+          <t>37164</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58646</t>
+          <t>58589</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>50757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>73298</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92927</t>
+          <t>93815</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126094</t>
+          <t>125830</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210990</t>
+          <t>211047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>232472</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183844</t>
+          <t>183758</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205738</t>
+          <t>206299</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>400598</t>
+          <t>400862</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>433765</t>
+          <t>432877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22923</t>
+          <t>22625</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49619</t>
+          <t>48377</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56886</t>
+          <t>57696</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>508663</t>
+          <t>548124</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86112</t>
+          <t>86074</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>744103</t>
+          <t>704376</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>574660</t>
+          <t>575902</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>601356</t>
+          <t>601654</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>340602</t>
+          <t>301141</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>792379</t>
+          <t>791569</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>729441</t>
+          <t>769168</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1387432</t>
+          <t>1387470</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71405</t>
+          <t>66117</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>216387</t>
+          <t>215118</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>201294</t>
+          <t>199770</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>243346</t>
+          <t>242880</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>231179</t>
+          <t>246266</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>449981</t>
+          <t>451538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>712333</t>
+          <t>713602</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>857315</t>
+          <t>862603</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>474385</t>
+          <t>474851</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>516437</t>
+          <t>517961</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1196471</t>
+          <t>1194914</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1415273</t>
+          <t>1400186</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>332435</t>
+          <t>323099</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>462865</t>
+          <t>461845</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>608615</t>
+          <t>605896</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1348448</t>
+          <t>1323806</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>995109</t>
+          <t>1002271</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1864797</t>
+          <t>1713776</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2996952</t>
+          <t>2997972</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3127382</t>
+          <t>3136718</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2363832</t>
+          <t>2388474</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3103665</t>
+          <t>3106384</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5307300</t>
+          <t>5458321</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6176988</t>
+          <t>6169826</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80441</t>
+          <t>79037</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111242</t>
+          <t>110360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95149</t>
+          <t>94813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129181</t>
+          <t>128352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>183856</t>
+          <t>186195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>229810</t>
+          <t>231074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161768</t>
+          <t>162650</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>192569</t>
+          <t>193973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131657</t>
+          <t>132486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>165689</t>
+          <t>166025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>304038</t>
+          <t>302774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>349992</t>
+          <t>347653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95210</t>
+          <t>94949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>136187</t>
+          <t>132762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135248</t>
+          <t>135673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176604</t>
+          <t>176851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>299249</t>
+          <t>299008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356888</t>
+          <t>360313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397865</t>
+          <t>398126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327345</t>
+          <t>327098</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368701</t>
+          <t>368276</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>697775</t>
+          <t>698016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>756020</t>
+          <t>754939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91497</t>
+          <t>91186</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126345</t>
+          <t>123833</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103791</t>
+          <t>103000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138099</t>
+          <t>137608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206086</t>
+          <t>203234</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253378</t>
+          <t>253860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192501</t>
+          <t>195013</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227349</t>
+          <t>227660</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>197313</t>
+          <t>197804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231621</t>
+          <t>232412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>400880</t>
+          <t>400398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>448172</t>
+          <t>451024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85976</t>
+          <t>85490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123287</t>
+          <t>121787</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>125116</t>
+          <t>123789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158910</t>
+          <t>160860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221594</t>
+          <t>223469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272407</t>
+          <t>273671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235384</t>
+          <t>236884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272695</t>
+          <t>273181</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>212546</t>
+          <t>210596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246340</t>
+          <t>247667</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>457720</t>
+          <t>456456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>508533</t>
+          <t>506658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>36664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59363</t>
+          <t>61136</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50466</t>
+          <t>50923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77771</t>
+          <t>77133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92542</t>
+          <t>93083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130327</t>
+          <t>129509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143945</t>
+          <t>142172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167789</t>
+          <t>166644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129897</t>
+          <t>130535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157202</t>
+          <t>156745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>280649</t>
+          <t>281467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>318434</t>
+          <t>317893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79066</t>
+          <t>80234</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110324</t>
+          <t>110893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65532</t>
+          <t>67862</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96483</t>
+          <t>97557</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>154567</t>
+          <t>154588</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198848</t>
+          <t>199392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160487</t>
+          <t>159918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191745</t>
+          <t>190577</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181661</t>
+          <t>180587</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>212612</t>
+          <t>210282</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>350107</t>
+          <t>349563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>394388</t>
+          <t>394367</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>156569</t>
+          <t>155479</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200626</t>
+          <t>200527</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>225839</t>
+          <t>224434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>273610</t>
+          <t>275210</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>394243</t>
+          <t>396177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>460570</t>
+          <t>461362</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>414401</t>
+          <t>414500</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>458458</t>
+          <t>459548</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>364609</t>
+          <t>363009</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>412380</t>
+          <t>413785</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>792676</t>
+          <t>791884</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>859003</t>
+          <t>857069</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>190068</t>
+          <t>188872</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>240336</t>
+          <t>239046</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>218718</t>
+          <t>217372</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>267843</t>
+          <t>269239</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>419324</t>
+          <t>417737</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>493673</t>
+          <t>491170</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>503459</t>
+          <t>504749</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>553727</t>
+          <t>554923</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>515668</t>
+          <t>514272</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>564793</t>
+          <t>566139</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1033633</t>
+          <t>1036136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1107982</t>
+          <t>1109569</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,65%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>902370</t>
+          <t>907289</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1007998</t>
+          <t>1008885</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1112673</t>
+          <t>1109829</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1224850</t>
+          <t>1221313</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2052399</t>
+          <t>2046214</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2205057</t>
+          <t>2200666</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2268545</t>
+          <t>2267658</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2374173</t>
+          <t>2369254</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2154347</t>
+          <t>2157884</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2266524</t>
+          <t>2269368</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4450684</t>
+          <t>4455075</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4603342</t>
+          <t>4609527</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117639</t>
+          <t>115801</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150863</t>
+          <t>150754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144050</t>
+          <t>143006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>180936</t>
+          <t>178551</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>269947</t>
+          <t>269835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>317185</t>
+          <t>318499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143875</t>
+          <t>143984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177099</t>
+          <t>178937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106309</t>
+          <t>108694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143195</t>
+          <t>144239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>264798</t>
+          <t>263484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>312036</t>
+          <t>312148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203071</t>
+          <t>204416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>251812</t>
+          <t>249405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239211</t>
+          <t>240875</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>285255</t>
+          <t>288897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>459885</t>
+          <t>458582</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>526140</t>
+          <t>521930</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>253715</t>
+          <t>256122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>302456</t>
+          <t>301111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>238510</t>
+          <t>234868</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>284554</t>
+          <t>282890</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>503152</t>
+          <t>507362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>569407</t>
+          <t>570710</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126696</t>
+          <t>125030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163230</t>
+          <t>161250</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154641</t>
+          <t>153684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195353</t>
+          <t>194151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>293073</t>
+          <t>293007</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344993</t>
+          <t>344677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160816</t>
+          <t>162796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>197350</t>
+          <t>199016</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145667</t>
+          <t>146869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186379</t>
+          <t>187336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320073</t>
+          <t>320389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371993</t>
+          <t>372059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,94%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164909</t>
+          <t>165359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>206403</t>
+          <t>207133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196713</t>
+          <t>197896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236852</t>
+          <t>236132</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>374086</t>
+          <t>374787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>435352</t>
+          <t>431354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167579</t>
+          <t>166849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209073</t>
+          <t>208623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152099</t>
+          <t>152819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192238</t>
+          <t>191055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327581</t>
+          <t>331579</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388847</t>
+          <t>388146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85582</t>
+          <t>86930</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115008</t>
+          <t>117512</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108821</t>
+          <t>108561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138665</t>
+          <t>139398</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200353</t>
+          <t>204147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245585</t>
+          <t>247108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97610</t>
+          <t>95106</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127036</t>
+          <t>125688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80926</t>
+          <t>80193</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110770</t>
+          <t>111030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186624</t>
+          <t>185101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231856</t>
+          <t>228062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>106240</t>
+          <t>106914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140177</t>
+          <t>140144</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>127516</t>
+          <t>126824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160053</t>
+          <t>161462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>243938</t>
+          <t>242743</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>290855</t>
+          <t>290781</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133804</t>
+          <t>133837</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167741</t>
+          <t>167067</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119978</t>
+          <t>118569</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152515</t>
+          <t>153207</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>263157</t>
+          <t>263231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>310074</t>
+          <t>311269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>266519</t>
+          <t>268640</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>321406</t>
+          <t>323316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>307562</t>
+          <t>308029</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>363395</t>
+          <t>362478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>595457</t>
+          <t>591378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>668053</t>
+          <t>667831</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>341382</t>
+          <t>339472</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>396269</t>
+          <t>394148</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>330458</t>
+          <t>331375</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386291</t>
+          <t>385824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>688588</t>
+          <t>688810</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>761184</t>
+          <t>765263</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>294932</t>
+          <t>297175</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>355138</t>
+          <t>354009</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>389886</t>
+          <t>386087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>444985</t>
+          <t>446998</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>700057</t>
+          <t>700793</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>779444</t>
+          <t>779978</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,66%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>423960</t>
+          <t>425089</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>484166</t>
+          <t>481923</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>378868</t>
+          <t>376855</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>433967</t>
+          <t>437766</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>823507</t>
+          <t>822973</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>902894</t>
+          <t>902158</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1475400</t>
+          <t>1473734</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1592229</t>
+          <t>1595276</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1777181</t>
+          <t>1775443</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1901415</t>
+          <t>1895160</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3291292</t>
+          <t>3288658</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3461983</t>
+          <t>3459538</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1834550</t>
+          <t>1831503</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1951379</t>
+          <t>1953045</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1656894</t>
+          <t>1663149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1781128</t>
+          <t>1782866</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3523105</t>
+          <t>3525550</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3693796</t>
+          <t>3696430</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94467</t>
+          <t>92840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130460</t>
+          <t>129509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103328</t>
+          <t>103936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138804</t>
+          <t>136924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208111</t>
+          <t>209241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256803</t>
+          <t>258095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163301</t>
+          <t>164252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>199294</t>
+          <t>200921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149899</t>
+          <t>151779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185375</t>
+          <t>184767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>325661</t>
+          <t>324369</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>374353</t>
+          <t>373223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114031</t>
+          <t>114134</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154202</t>
+          <t>154937</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158638</t>
+          <t>158872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202394</t>
+          <t>200305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>280619</t>
+          <t>283019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>340275</t>
+          <t>343830</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348373</t>
+          <t>347638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>388544</t>
+          <t>388441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320690</t>
+          <t>322779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364446</t>
+          <t>364212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>685384</t>
+          <t>681829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745040</t>
+          <t>742640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,41%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70218</t>
+          <t>68520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101577</t>
+          <t>98800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85668</t>
+          <t>85581</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119854</t>
+          <t>118196</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163130</t>
+          <t>164877</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207515</t>
+          <t>208997</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>216988</t>
+          <t>219765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>248347</t>
+          <t>250045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>216455</t>
+          <t>218113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250641</t>
+          <t>250728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>447359</t>
+          <t>445877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>491744</t>
+          <t>489997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93898</t>
+          <t>94783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130319</t>
+          <t>130072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134841</t>
+          <t>134959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>174004</t>
+          <t>175366</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>237340</t>
+          <t>237757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>294161</t>
+          <t>293514</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239645</t>
+          <t>239892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276066</t>
+          <t>275181</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>213279</t>
+          <t>211917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>252442</t>
+          <t>252324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>463086</t>
+          <t>463733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519907</t>
+          <t>519490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76992</t>
+          <t>74813</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105081</t>
+          <t>103987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88171</t>
+          <t>88700</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116932</t>
+          <t>117426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172766</t>
+          <t>172871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213452</t>
+          <t>213347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106140</t>
+          <t>107234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134229</t>
+          <t>136408</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101655</t>
+          <t>101161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130416</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216356</t>
+          <t>216461</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257042</t>
+          <t>256937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61764</t>
+          <t>63381</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91484</t>
+          <t>91747</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74569</t>
+          <t>76195</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>106991</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>146318</t>
+          <t>147809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>190570</t>
+          <t>192456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>171639</t>
+          <t>171376</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201359</t>
+          <t>199742</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>166038</t>
+          <t>166124</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>198546</t>
+          <t>196920</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>345668</t>
+          <t>343782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>389920</t>
+          <t>388429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>151191</t>
+          <t>151410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197658</t>
+          <t>199793</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>227142</t>
+          <t>226972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>278123</t>
+          <t>281603</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>390557</t>
+          <t>393676</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>459785</t>
+          <t>460703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>458900</t>
+          <t>456765</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>505367</t>
+          <t>505148</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>413171</t>
+          <t>409691</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>464152</t>
+          <t>464322</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>888067</t>
+          <t>887149</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>957295</t>
+          <t>954176</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>251279</t>
+          <t>253415</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>306687</t>
+          <t>304978</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>347754</t>
+          <t>345135</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>404591</t>
+          <t>403728</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>616966</t>
+          <t>617119</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>693369</t>
+          <t>693488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>471896</t>
+          <t>473605</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>527304</t>
+          <t>525168</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>421576</t>
+          <t>422439</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>478413</t>
+          <t>481032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>911381</t>
+          <t>911262</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>987784</t>
+          <t>987631</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1008815</t>
+          <t>1007320</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1117687</t>
+          <t>1112032</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1316269</t>
+          <t>1312919</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1436404</t>
+          <t>1430779</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2353450</t>
+          <t>2351851</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2514349</t>
+          <t>2520436</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2276663</t>
+          <t>2282318</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2385535</t>
+          <t>2387030</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2108138</t>
+          <t>2113763</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2228273</t>
+          <t>2231623</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4424543</t>
+          <t>4418456</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4585442</t>
+          <t>4587041</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18206</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>27694</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24737</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17739</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>36235</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42942</t>
+          <t>47216</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33345</t>
+          <t>37388</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54983</t>
+          <t>58817</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>293237</t>
+          <t>300300</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283522</t>
+          <t>291151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>299820</t>
+          <t>307083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>264898</t>
+          <t>287391</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257206</t>
+          <t>279826</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271896</t>
+          <t>295523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>558135</t>
+          <t>587690</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>576089</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567732</t>
+          <t>597518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55849</t>
+          <t>62557</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41478</t>
+          <t>45689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73724</t>
+          <t>82690</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>101314</t>
+          <t>112742</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86247</t>
+          <t>96179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116862</t>
+          <t>130928</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>157163</t>
+          <t>175299</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135057</t>
+          <t>153425</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179770</t>
+          <t>199206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>462541</t>
+          <t>468090</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>444666</t>
+          <t>447957</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>476912</t>
+          <t>484958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>413655</t>
+          <t>433752</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>398107</t>
+          <t>415566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>428722</t>
+          <t>450315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>876196</t>
+          <t>901842</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>853589</t>
+          <t>877935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>898302</t>
+          <t>923716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37994</t>
+          <t>39084</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49567</t>
+          <t>51953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>45707</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>58173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>84256</t>
+          <t>84792</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71693</t>
+          <t>69403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101943</t>
+          <t>98988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>278056</t>
+          <t>276909</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>266483</t>
+          <t>264040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287377</t>
+          <t>286751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>302866</t>
+          <t>310674</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290938</t>
+          <t>298208</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312845</t>
+          <t>319744</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>580922</t>
+          <t>587583</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>563235</t>
+          <t>573387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>593485</t>
+          <t>602972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48647</t>
+          <t>61134</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>42983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67761</t>
+          <t>81296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62782</t>
+          <t>71947</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37606</t>
+          <t>58884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83124</t>
+          <t>87411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>111429</t>
+          <t>133081</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78613</t>
+          <t>111521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136445</t>
+          <t>157364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>263910</t>
+          <t>312011</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>244796</t>
+          <t>291849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>277621</t>
+          <t>330162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>412936</t>
+          <t>350014</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>392594</t>
+          <t>334550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>438112</t>
+          <t>363077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>676845</t>
+          <t>662026</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651829</t>
+          <t>637743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>709661</t>
+          <t>683586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>23234</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29430</t>
+          <t>32884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24348</t>
+          <t>27329</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13099</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34029</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43639</t>
+          <t>50562</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>40535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55320</t>
+          <t>63260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>159451</t>
+          <t>182431</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>149312</t>
+          <t>172781</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165421</t>
+          <t>189964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>234431</t>
+          <t>201589</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224750</t>
+          <t>194225</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>245680</t>
+          <t>207648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>393882</t>
+          <t>384020</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382201</t>
+          <t>371322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407719</t>
+          <t>394047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>49500</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>39234</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58589</t>
+          <t>62206</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60864</t>
+          <t>62549</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50757</t>
+          <t>52430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73298</t>
+          <t>73627</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>108557</t>
+          <t>112048</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93815</t>
+          <t>96620</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>125830</t>
+          <t>128259</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>221943</t>
+          <t>221207</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211047</t>
+          <t>208501</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232472</t>
+          <t>231473</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>196192</t>
+          <t>201201</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183758</t>
+          <t>190123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>206299</t>
+          <t>211320</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>418135</t>
+          <t>422409</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>400862</t>
+          <t>406198</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>432877</t>
+          <t>437837</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33209</t>
+          <t>41201</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22625</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48377</t>
+          <t>56017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>251460</t>
+          <t>63507</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57696</t>
+          <t>51028</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>548124</t>
+          <t>78875</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>284668</t>
+          <t>104709</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86074</t>
+          <t>86512</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>704376</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>591070</t>
+          <t>678486</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>575902</t>
+          <t>663670</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>601654</t>
+          <t>691564</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>597805</t>
+          <t>708550</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301141</t>
+          <t>693182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>791569</t>
+          <t>721029</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1188876</t>
+          <t>1387035</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>769168</t>
+          <t>1365429</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1387470</t>
+          <t>1405232</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>152045</t>
+          <t>183620</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66117</t>
+          <t>159726</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>215118</t>
+          <t>209898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>221525</t>
+          <t>261303</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>199770</t>
+          <t>239330</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>242880</t>
+          <t>286915</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>373570</t>
+          <t>444923</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246266</t>
+          <t>413682</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>451538</t>
+          <t>482710</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>776675</t>
+          <t>614452</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>713602</t>
+          <t>588174</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>862603</t>
+          <t>638346</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>496206</t>
+          <t>570028</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>474851</t>
+          <t>544416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>517961</t>
+          <t>592001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1272882</t>
+          <t>1184480</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1194914</t>
+          <t>1146693</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1400186</t>
+          <t>1215721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>74,61%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>412934</t>
+          <t>478875</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>323099</t>
+          <t>438065</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>461845</t>
+          <t>523629</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>793292</t>
+          <t>673754</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>605896</t>
+          <t>633462</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1323806</t>
+          <t>716404</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1206225</t>
+          <t>1152629</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1002271</t>
+          <t>1096644</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1713776</t>
+          <t>1221522</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3046883</t>
+          <t>3053887</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2997972</t>
+          <t>3009133</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3136718</t>
+          <t>3094697</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2918988</t>
+          <t>3063200</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2388474</t>
+          <t>3020550</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3106384</t>
+          <t>3103492</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5965872</t>
+          <t>6117087</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5458321</t>
+          <t>6048194</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6169826</t>
+          <t>6173072</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
